--- a/材料清单.xlsx
+++ b/材料清单.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\25710\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\25710\LEDParkingGuidanceDisplay\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84A4C272-5E8B-4928-A5F7-9D36AE261259}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDE718DE-8EA9-43CA-9FBA-4FD5755FF69D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t>编号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -63,10 +63,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>WS2812B可编程灯带</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>WX6.0-6PS带帽微型滑环</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -76,6 +72,73 @@
   </si>
   <si>
     <t>CH-2接线端子</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>详细配置说明</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DC接口</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5V，白板裸板，1m96灯</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WS2812B灯带</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ESP8266</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CH340芯片-安卓接口</t>
+  </si>
+  <si>
+    <t>铜箔双面导电胶带</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>杜邦线带鳄鱼夹（母头）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>杜邦线带鳄鱼夹（公头）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>外径6mm 6路1A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>钢片，2进2出，0.5~2.5平方</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>插拔式接线端子</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>15EDGRKP-3.81MM 2-24P空中对接，免焊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>oled屏幕</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>测试传感器时显示信息用，不作旋转LED装置的显示用</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TYPEC母座转插针DIP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STLink</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -107,7 +170,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -115,15 +178,37 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -404,111 +489,225 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="25.796875" customWidth="1"/>
+    <col min="2" max="2" width="32.33203125" customWidth="1"/>
+    <col min="3" max="3" width="51.9296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A2" s="1">
+      <c r="C1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" s="2"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A2" s="3">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A3" s="1">
+      <c r="C2" s="3"/>
+      <c r="D2" s="2"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A3" s="3">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" s="2"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A4" s="3">
         <v>3</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A4" s="1">
+      <c r="B4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="3"/>
+      <c r="D4" s="2"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A5" s="3">
         <v>4</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A5" s="1">
+      <c r="B5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="C5" s="3"/>
+      <c r="D5" s="2"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A6" s="3">
         <v>5</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A6" s="1">
+      <c r="B6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="C6" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="2"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A7" s="3">
         <v>6</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A7" s="1">
+      <c r="B7" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="C7" s="3"/>
+      <c r="D7" s="2"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A8" s="3">
         <v>7</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A8" s="1">
+      <c r="B8" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="C8" s="3"/>
+      <c r="D8" s="2"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A9" s="3">
         <v>8</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A9" s="1">
+      <c r="B9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="C9" s="3"/>
+      <c r="D9" s="2"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A10" s="3">
         <v>9</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A10" s="1">
+      <c r="B10" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" s="2"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A11" s="3">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="C11" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11" s="2"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A12" s="3">
+        <v>11</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A11" s="1">
-        <v>10</v>
-      </c>
-      <c r="B11" s="1" t="s">
+      <c r="C12" s="3"/>
+      <c r="D12" s="2"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A13" s="3">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A12" s="1">
-        <v>11</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
+      <c r="C13" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D13" s="2"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A14" s="3">
+        <v>13</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D14" s="2"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A15" s="3">
+        <v>14</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="3"/>
+      <c r="D15" s="2"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A16" s="3">
+        <v>15</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" s="3"/>
+      <c r="D16" s="2"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A17" s="3">
+        <v>16</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" s="3"/>
+      <c r="D17" s="2"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A18" s="3">
+        <v>17</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D18" s="2"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A19" s="3">
+        <v>18</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A20" s="3">
+        <v>19</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
